--- a/healthcare_forms/016_healthcare_policy_literacy_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/016_healthcare_policy_literacy_survey--healthcare_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact_info_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Contact Info 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_info_additional</t>
+          <t>contact_info_additional_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Contact Info</t>
+          <t>Contact Info Additional 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
